--- a/src/ExcelsiorAspose.Tests/Headings.Fluent.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/Headings.Fluent.verified.xlsx
@@ -80,8 +80,15 @@
   <numFmts count="1">
     <numFmt numFmtId="177" formatCode="yyyy-MM-dd"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -116,8 +123,9 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -512,127 +520,126 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="15.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="18.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="19.7142857142857" customWidth="1"/>
-    <col min="4" max="4" width="12.7142857142857" customWidth="1"/>
-    <col min="5" max="5" width="16.7142857142857" customWidth="1"/>
-    <col min="6" max="6" width="11.7142857142857" customWidth="1"/>
+    <col min="1" max="1" width="16.7142857142857" customWidth="1"/>
+    <col min="2" max="3" width="19.7142857142857" customWidth="1"/>
+    <col min="4" max="4" width="13.7142857142857" customWidth="1"/>
+    <col min="5" max="5" width="17.7142857142857" customWidth="1"/>
+    <col min="6" max="6" width="12.7142857142857" customWidth="1"/>
     <col min="7" max="7" width="10.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14" customHeight="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="14" customHeight="1">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="3">
         <v>43845</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="2">
         <v>75000</v>
       </c>
-      <c r="F2" s="1" t="b">
+      <c r="F2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="14" customHeight="1">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="3">
         <v>43546</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="2">
         <v>120000</v>
       </c>
-      <c r="F3" s="1" t="b">
+      <c r="F3" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14" customHeight="1">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="3">
         <v>44387</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="2">
         <v>45000</v>
       </c>
-      <c r="F4" s="1" t="b">
+      <c r="F4" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="14" customHeight="1">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>43409</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="2">
         <v>95000</v>
       </c>
-      <c r="F5" s="1" t="b">
+      <c r="F5" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="2" t="s">
         <v>17</v>
       </c>
     </row>

--- a/src/ExcelsiorAspose.Tests/Headings.Fluent.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/Headings.Fluent.verified.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="2" r:id="DeterministicId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$5</definedName>

--- a/src/ExcelsiorAspose.Tests/Headings.Fluent.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/Headings.Fluent.verified.xlsx
@@ -528,7 +528,7 @@
     <col min="7" max="7" width="10.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="14" customHeight="1">
+    <row r="1" spans="1:7" ht="16" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -551,7 +551,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="14" customHeight="1">
+    <row r="2" spans="1:7" ht="16" customHeight="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -574,7 +574,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="14" customHeight="1">
+    <row r="3" spans="1:7" ht="16" customHeight="1">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -597,7 +597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="14" customHeight="1">
+    <row r="4" spans="1:7" ht="16" customHeight="1">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -620,7 +620,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="14" customHeight="1">
+    <row r="5" spans="1:7" ht="16" customHeight="1">
       <c r="A5" s="2">
         <v>4</v>
       </c>

--- a/src/ExcelsiorAspose.Tests/Headings.Fluent.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/Headings.Fluent.verified.xlsx
@@ -528,7 +528,7 @@
     <col min="7" max="7" width="10.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16" customHeight="1">
+    <row r="1" spans="1:7" ht="14" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -551,7 +551,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="16" customHeight="1">
+    <row r="2" spans="1:7" ht="14" customHeight="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -574,7 +574,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16" customHeight="1">
+    <row r="3" spans="1:7" ht="14" customHeight="1">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -597,7 +597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16" customHeight="1">
+    <row r="4" spans="1:7" ht="14" customHeight="1">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -620,7 +620,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16" customHeight="1">
+    <row r="5" spans="1:7" ht="14" customHeight="1">
       <c r="A5" s="2">
         <v>4</v>
       </c>
